--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487066_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487066_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. DIEYE</t>
+          <t>E. MADINABEITIA GARCIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8659</v>
+        <v>1.6262</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2854</v>
+        <v>0.848</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4196</v>
+        <v>0.7782</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7753</v>
+        <v>0.1328</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.237</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8414</v>
+        <v>-0.1042</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7613</v>
+        <v>1.7469</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4347</v>
+        <v>0.9986</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3267</v>
+        <v>0.7483</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0139</v>
+        <v>-1.6141</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5009</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5148</v>
+        <v>-0.8526</v>
       </c>
       <c r="P2" t="n">
-        <v>0.579</v>
+        <v>-0.965</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.193</v>
+        <v>-3.2811</v>
       </c>
       <c r="R2" t="n">
-        <v>0.772</v>
+        <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2604</v>
+        <v>0.4938</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2829</v>
+        <v>-0.0737</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0225</v>
+        <v>0.5674</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.228</v>
+        <v>1.9647</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.228</v>
+        <v>-0.4912</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MADINABEITIA GARCIA</t>
+          <t>M. DIEYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4523</v>
+        <v>1.0196</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0314</v>
+        <v>1.3856</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4837</v>
+        <v>-0.366</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1328</v>
+        <v>1.7753</v>
       </c>
       <c r="H3" t="n">
-        <v>0.237</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1042</v>
+        <v>1.8414</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7469</v>
+        <v>1.7613</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9986</v>
+        <v>0.4347</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7483</v>
+        <v>1.3267</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6141</v>
+        <v>0.0139</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.5009</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8526</v>
+        <v>0.5148</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.965</v>
+        <v>0.579</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.2811</v>
+        <v>-0.193</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3161</v>
+        <v>0.772</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6802</v>
+        <v>-0.1068</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.1828</v>
       </c>
       <c r="U3" t="n">
-        <v>0.273</v>
+        <v>0.076</v>
       </c>
       <c r="V3" t="n">
-        <v>1.9647</v>
+        <v>-1.228</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4912</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1126</v>
+        <v>0.419</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0941</v>
+        <v>0.2658</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2067</v>
+        <v>0.1531</v>
       </c>
       <c r="G4" t="n">
         <v>0.6717</v>
@@ -766,13 +766,13 @@
         <v>0.772</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1428</v>
+        <v>0.4491</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.2846</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2181</v>
+        <v>0.1646</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1228</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>J. DOSS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0409</v>
+        <v>0.2615</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2097</v>
+        <v>-0.9708</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2506</v>
+        <v>1.2323</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0249</v>
+        <v>2.4779</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2845</v>
+        <v>-0.1026</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7405</v>
+        <v>2.5805</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0639</v>
+        <v>3.471</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3159</v>
+        <v>0.305</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2521</v>
+        <v>3.166</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9611</v>
+        <v>-0.9931</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9685</v>
+        <v>-0.4076</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9925</v>
+        <v>-0.5855</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2811</v>
+        <v>-4.2462</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3161</v>
+        <v>2.1231</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6644</v>
+        <v>0.6838</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0497</v>
+        <v>-0.1956</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6147</v>
+        <v>0.8794</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3664</v>
+        <v>-0.7771</v>
       </c>
       <c r="W5" t="n">
-        <v>2.0856</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7192</v>
+        <v>-0.7771</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. DOSS</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3978</v>
+        <v>0.1738</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5498</v>
+        <v>-1.396</v>
       </c>
       <c r="F6" t="n">
-        <v>1.152</v>
+        <v>1.5698</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4779</v>
+        <v>-0.9704</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1026</v>
+        <v>0.7504</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5805</v>
+        <v>-1.7208</v>
       </c>
       <c r="J6" t="n">
-        <v>3.471</v>
+        <v>-0.7446</v>
       </c>
       <c r="K6" t="n">
-        <v>0.305</v>
+        <v>1.0711</v>
       </c>
       <c r="L6" t="n">
-        <v>3.166</v>
+        <v>-1.8157</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9931</v>
+        <v>-0.2258</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4076</v>
+        <v>-0.3207</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5855</v>
+        <v>0.0949</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.1231</v>
+        <v>0.772</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.2462</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1231</v>
+        <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0244</v>
+        <v>0.0862</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7746</v>
+        <v>-0.2581</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7991</v>
+        <v>0.3443</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7771</v>
+        <v>0.2859</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7771</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4964</v>
+        <v>-0.2436</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7274</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.231</v>
+        <v>0.3648</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6147</v>
@@ -1000,13 +1000,13 @@
         <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3113</v>
+        <v>0.5642</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1322</v>
+        <v>0.2512</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1791</v>
+        <v>0.313</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.547</v>
+        <v>-1.1975</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9562</v>
+        <v>-0.8324</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4091</v>
+        <v>-0.3651</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9704</v>
+        <v>-2.0249</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7504</v>
+        <v>-1.2845</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7208</v>
+        <v>-0.7405</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7446</v>
+        <v>-0.0639</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0711</v>
+        <v>-0.3159</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8157</v>
+        <v>0.2521</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2258</v>
+        <v>-1.9611</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3207</v>
+        <v>-0.9685</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0949</v>
+        <v>-0.9925</v>
       </c>
       <c r="P8" t="n">
-        <v>0.772</v>
+        <v>-0.965</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-3.2811</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7371</v>
+        <v>2.3161</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6346000000000001</v>
+        <v>1.4261</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8183</v>
+        <v>0.427</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1837</v>
+        <v>0.999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2859</v>
+        <v>0.3664</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5717</v>
+        <v>2.0856</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2859</v>
+        <v>-1.7192</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0958</v>
+        <v>-2.4055</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7406</v>
+        <v>-1.6982</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3552</v>
+        <v>-0.7073</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3871</v>
+        <v>0.6156</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5142</v>
+        <v>0.1615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1271</v>
+        <v>0.4541</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2938</v>
+        <v>0.5888</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2938</v>
+        <v>0.6624</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.0735</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.09329999999999999</v>
+        <v>0.0268</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2204</v>
+        <v>-0.5009</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1271</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.579</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.158</v>
+        <v>-1.9301</v>
       </c>
       <c r="R9" t="n">
         <v>0.579</v>
       </c>
       <c r="S9" t="n">
-        <v>0.893</v>
+        <v>-0.0737</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7112000000000001</v>
+        <v>-0.3569</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1818</v>
+        <v>0.2832</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0226</v>
+        <v>-1.5964</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0226</v>
+        <v>-1.5964</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4382</v>
+        <v>-2.4696</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7577</v>
+        <v>-2.1412</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6806</v>
+        <v>-0.3284</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6156</v>
+        <v>-1.3871</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1615</v>
+        <v>-1.5142</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4541</v>
+        <v>0.1271</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5888</v>
+        <v>-1.2938</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6624</v>
+        <v>-1.2938</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0735</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0268</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5009</v>
+        <v>-0.2204</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.1271</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3511</v>
+        <v>-0.579</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9301</v>
+        <v>-1.158</v>
       </c>
       <c r="R10" t="n">
         <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1064</v>
+        <v>0.5192</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4164</v>
+        <v>0.3107</v>
       </c>
       <c r="U10" t="n">
-        <v>0.31</v>
+        <v>0.2085</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5964</v>
+        <v>-1.0226</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5964</v>
+        <v>-1.0226</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2762</v>
+        <v>-6.0713</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5883</v>
+        <v>-5.3299</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6879</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1105</v>
@@ -1312,13 +1312,13 @@
         <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0629</v>
+        <v>0.2677</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7403</v>
+        <v>-0.0013</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3225</v>
+        <v>0.269</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9824000000000001</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.779700000000002</v>
+        <v>-8.8874</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.3698</v>
+        <v>-10.4775</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5898</v>
+        <v>1.59</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4343</v>
+        <v>-0.4342999999999997</v>
       </c>
       <c r="H12" t="n">
         <v>-4.4401</v>
@@ -1366,10 +1366,10 @@
         <v>6.4</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7700999999999997</v>
+        <v>0.7700999999999998</v>
       </c>
       <c r="L12" t="n">
-        <v>5.630300000000001</v>
+        <v>5.6303</v>
       </c>
       <c r="M12" t="n">
         <v>-6.8347</v>
@@ -1381,7 +1381,7 @@
         <v>-1.6244</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.650400000000001</v>
+        <v>-9.650399999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-22.1958</v>
@@ -1390,13 +1390,13 @@
         <v>12.5454</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4172</v>
+        <v>4.309599999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6871999999999998</v>
+        <v>0.2051</v>
       </c>
       <c r="U12" t="n">
-        <v>4.1045</v>
+        <v>4.1044</v>
       </c>
       <c r="V12" t="n">
         <v>-3.1123</v>
@@ -1405,7 +1405,7 @@
         <v>5.1132</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.2256</v>
+        <v>-8.225599999999998</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4035</v>
+        <v>4.9316</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1188</v>
+        <v>5.2189</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7153</v>
+        <v>-0.2873</v>
       </c>
       <c r="G13" t="n">
         <v>3.8808</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8295</v>
+        <v>-0.3014</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2102</v>
+        <v>-0.11</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6194</v>
+        <v>-0.1914</v>
       </c>
       <c r="V13" t="n">
         <v>0.5802</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>A. ALDA IRAOLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0907</v>
+        <v>4.0625</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2613</v>
+        <v>2.5796</v>
       </c>
       <c r="F14" t="n">
-        <v>4.352</v>
+        <v>1.4829</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.3133</v>
+        <v>2.5786</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8921</v>
+        <v>0.9749</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.4212</v>
+        <v>1.6037</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.3872</v>
+        <v>2.9524</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.092</v>
+        <v>1.6093</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2952</v>
+        <v>1.3431</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9261</v>
+        <v>-0.3738</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1999</v>
+        <v>-0.6344</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.126</v>
+        <v>0.2606</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1231</v>
+        <v>1.7371</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.0532</v>
+        <v>1.7371</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2605</v>
+        <v>-0.2531</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2419</v>
+        <v>-0.3728</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5024</v>
+        <v>0.1196</v>
       </c>
       <c r="V14" t="n">
-        <v>4.0205</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2979</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ALDA IRAOLA</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6084</v>
+        <v>3.3944</v>
       </c>
       <c r="E15" t="n">
-        <v>2.179</v>
+        <v>-0.6619</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4294</v>
+        <v>4.0562</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5786</v>
+        <v>-3.3133</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9749</v>
+        <v>-0.8921</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6037</v>
+        <v>-2.4212</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9524</v>
+        <v>-2.3872</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6093</v>
+        <v>-1.092</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3431</v>
+        <v>-1.2952</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3738</v>
+        <v>-0.9261</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6344</v>
+        <v>0.1999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2606</v>
+        <v>-1.126</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7371</v>
+        <v>2.1231</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7371</v>
+        <v>4.0532</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7072000000000001</v>
+        <v>0.5642</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7733</v>
+        <v>-0.6424</v>
       </c>
       <c r="U15" t="n">
-        <v>0.06610000000000001</v>
+        <v>1.2066</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4.0205</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>4.2979</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2774</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9578</v>
+        <v>1.8606</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8749</v>
+        <v>-0.4557</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8327</v>
+        <v>2.3162</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6309</v>
+        <v>-1.0536</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5072</v>
+        <v>0.091</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1381</v>
+        <v>-1.1446</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1564</v>
+        <v>-0.2267</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6005</v>
+        <v>0.3517</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7569</v>
+        <v>-0.5783</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4745</v>
+        <v>-0.8269</v>
       </c>
       <c r="N16" t="n">
-        <v>0.09329999999999999</v>
+        <v>-0.2607</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3813</v>
+        <v>-0.5662</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3511</v>
+        <v>2.8951</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2811</v>
+        <v>2.8951</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2617</v>
+        <v>0.0106</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3291</v>
+        <v>-0.229</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5909</v>
+        <v>0.2396</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2859</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5138</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5466</v>
+        <v>1.8369</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5558</v>
+        <v>-1.0752</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1024</v>
+        <v>2.912</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0536</v>
+        <v>0.6309</v>
       </c>
       <c r="H17" t="n">
-        <v>0.091</v>
+        <v>-0.5072</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1446</v>
+        <v>1.1381</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2267</v>
+        <v>0.1564</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3517</v>
+        <v>-0.6005</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5783</v>
+        <v>0.7569</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8269</v>
+        <v>0.4745</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2607</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5662</v>
+        <v>0.3813</v>
       </c>
       <c r="P17" t="n">
-        <v>2.8951</v>
+        <v>1.3511</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8951</v>
+        <v>3.2811</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3034</v>
+        <v>0.1408</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3291</v>
+        <v>-0.5294</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0258</v>
+        <v>0.6702</v>
       </c>
       <c r="V17" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.2859</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X17" t="n">
-        <v>0.008399999999999999</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2454</v>
+        <v>0.4097</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4695</v>
+        <v>0.6698</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7149</v>
+        <v>-0.2601</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7483</v>
@@ -1858,13 +1858,13 @@
         <v>2.5091</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6636</v>
+        <v>-0.0086</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5671</v>
+        <v>-0.3668</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0965</v>
+        <v>0.3582</v>
       </c>
       <c r="V18" t="n">
         <v>0.6224</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7865</v>
+        <v>-0.145</v>
       </c>
       <c r="E19" t="n">
         <v>-1.8426</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0561</v>
+        <v>1.6976</v>
       </c>
       <c r="G19" t="n">
         <v>1.4923</v>
@@ -1936,13 +1936,13 @@
         <v>2.1231</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2208</v>
+        <v>-0.5794</v>
       </c>
       <c r="T19" t="n">
         <v>-0.6993</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5215</v>
+        <v>0.12</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2859</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. IRASTORZA EZKIAGA</t>
+          <t>J. ELOSEGUI OLANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3262</v>
+        <v>-0.9258</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4299</v>
+        <v>-2.5191</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1037</v>
+        <v>1.5934</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1272</v>
+        <v>-1.712</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.028</v>
+        <v>0.3965</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0993</v>
+        <v>-2.1085</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3009</v>
+        <v>-1.8793</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3416</v>
+        <v>0.0828</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0407</v>
+        <v>-1.9621</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1737</v>
+        <v>0.1673</v>
       </c>
       <c r="N20" t="n">
         <v>0.3137</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.14</v>
+        <v>-0.1464</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.193</v>
+        <v>1.158</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.392</v>
+        <v>-0.3718</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1639</v>
+        <v>-0.6398</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.228</v>
+        <v>0.268</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ELOSEGUI OLANO</t>
+          <t>A. IRASTORZA EZKIAGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5673</v>
+        <v>-1.1124</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5191</v>
+        <v>-1.4299</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9519</v>
+        <v>0.3175</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.712</v>
+        <v>-0.1272</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3965</v>
+        <v>-0.028</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1085</v>
+        <v>-0.0993</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.8793</v>
+        <v>-0.3009</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0828</v>
+        <v>-0.3416</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9621</v>
+        <v>0.0407</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1673</v>
+        <v>0.1737</v>
       </c>
       <c r="N21" t="n">
         <v>0.3137</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1464</v>
+        <v>-0.14</v>
       </c>
       <c r="P21" t="n">
-        <v>1.158</v>
+        <v>-0.193</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>1.158</v>
+        <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0133</v>
+        <v>-0.1781</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6398</v>
+        <v>-0.1639</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3735</v>
+        <v>-0.0142</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.902</v>
+        <v>-1.8623</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8736</v>
+        <v>-2.0739</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0284</v>
+        <v>0.2116</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1936</v>
@@ -2170,13 +2170,13 @@
         <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1904</v>
+        <v>0.23</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1507</v>
+        <v>-0.351</v>
       </c>
       <c r="U22" t="n">
-        <v>0.341</v>
+        <v>0.581</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9336</v>
@@ -2203,25 +2203,25 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.7796</v>
+        <v>12.4502</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5899</v>
+        <v>-1.590000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>11.3696</v>
+        <v>14.04</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4345999999999999</v>
+        <v>0.4345999999999994</v>
       </c>
       <c r="H23" t="n">
-        <v>4.440200000000001</v>
+        <v>4.4402</v>
       </c>
       <c r="I23" t="n">
         <v>-4.0057</v>
       </c>
       <c r="J23" t="n">
-        <v>6.834700000000001</v>
+        <v>6.8347</v>
       </c>
       <c r="K23" t="n">
         <v>5.2102</v>
@@ -2230,16 +2230,16 @@
         <v>1.6247</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.400300000000001</v>
+        <v>-6.4003</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7699999999999998</v>
+        <v>-0.77</v>
       </c>
       <c r="O23" t="n">
         <v>-5.6301</v>
       </c>
       <c r="P23" t="n">
-        <v>9.650499999999999</v>
+        <v>9.650500000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-12.5454</v>
@@ -2248,13 +2248,13 @@
         <v>22.1959</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.4172</v>
+        <v>-0.7468</v>
       </c>
       <c r="T23" t="n">
         <v>-4.1044</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6873000000000001</v>
+        <v>3.3576</v>
       </c>
       <c r="V23" t="n">
         <v>3.1121</v>
